--- a/product-definitions/spreadsheet/flux-estimates.xlsx
+++ b/product-definitions/spreadsheet/flux-estimates.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="91">
   <si>
     <t>Name</t>
   </si>
@@ -107,10 +107,10 @@
     <t>buoyancy_flux</t>
   </si>
   <si>
-    <t>J m-2 s-1</t>
-  </si>
-  <si>
-    <t>Buoyancy Flux (&lt;w'Ts'&gt;)</t>
+    <t>W m-2</t>
+  </si>
+  <si>
+    <t>Buoyancy Flux (&lt;w'Ts'&gt;*rho*cp)</t>
   </si>
   <si>
     <t>cell_methods</t>
@@ -138,9 +138,6 @@
   </si>
   <si>
     <t>upward_sensible_heat_flux_in_air</t>
-  </si>
-  <si>
-    <t>W m-2</t>
   </si>
   <si>
     <t>Sensible heat flux</t>
@@ -310,7 +307,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -336,14 +333,9 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -361,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -397,35 +389,32 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2016,7 +2005,7 @@
       <c r="B38" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2033,7 +2022,7 @@
       <c r="B40" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="13" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2287,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" ht="12.0" customHeight="1">
@@ -2303,7 +2292,7 @@
         <v>16</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" ht="12.0" customHeight="1">
@@ -2351,7 +2340,7 @@
     </row>
     <row r="83" ht="12.0" customHeight="1">
       <c r="A83" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C83" s="10"/>
     </row>
@@ -2376,7 +2365,7 @@
         <v>2</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87" ht="12.0" customHeight="1">
@@ -2384,7 +2373,7 @@
         <v>15</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" ht="12.0" customHeight="1">
@@ -2392,7 +2381,7 @@
         <v>16</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="89" ht="12.0" customHeight="1">
@@ -2440,7 +2429,7 @@
     </row>
     <row r="95" ht="12.0" customHeight="1">
       <c r="A95" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C95" s="10"/>
     </row>
@@ -2465,7 +2454,7 @@
         <v>2</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="99" ht="12.0" customHeight="1">
@@ -2474,7 +2463,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="100" ht="12.0" customHeight="1">
@@ -2482,7 +2471,7 @@
         <v>16</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101" ht="12.0" customHeight="1">
@@ -2530,7 +2519,7 @@
     </row>
     <row r="107" ht="12.0" customHeight="1">
       <c r="A107" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C107" s="10"/>
     </row>
@@ -2555,7 +2544,7 @@
         <v>2</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="111" ht="12.0" customHeight="1">
@@ -2564,7 +2553,7 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="112" ht="12.0" customHeight="1">
@@ -2572,7 +2561,7 @@
         <v>16</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="113" ht="12.0" customHeight="1">
@@ -2620,7 +2609,7 @@
     </row>
     <row r="119" ht="12.0" customHeight="1">
       <c r="A119" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C119" s="10"/>
     </row>
@@ -2654,7 +2643,7 @@
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="124" ht="12.0" customHeight="1">
@@ -2662,7 +2651,7 @@
         <v>16</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="125" ht="12.0" customHeight="1">
@@ -2709,33 +2698,33 @@
       <c r="C130" s="10"/>
     </row>
     <row r="131" ht="12.0" customHeight="1">
-      <c r="A131" s="13" t="s">
+      <c r="A131" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B131" s="14"/>
+      <c r="C131" s="15"/>
+    </row>
+    <row r="132" ht="12.0" customHeight="1">
+      <c r="A132" s="14"/>
+      <c r="B132" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C132" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B131" s="13"/>
-      <c r="C131" s="14"/>
-    </row>
-    <row r="132" ht="12.0" customHeight="1">
-      <c r="A132" s="13"/>
-      <c r="B132" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C132" s="14" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="133" ht="12.0" customHeight="1">
-      <c r="A133" s="13"/>
-      <c r="B133" s="13" t="s">
+      <c r="A133" s="14"/>
+      <c r="B133" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C133" s="14" t="s">
+      <c r="C133" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="134" ht="12.0" customHeight="1">
-      <c r="A134" s="13"/>
-      <c r="B134" s="13" t="s">
+      <c r="A134" s="14"/>
+      <c r="B134" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C134" s="12">
@@ -2743,72 +2732,72 @@
       </c>
     </row>
     <row r="135" ht="12.0" customHeight="1">
-      <c r="A135" s="13"/>
-      <c r="B135" s="13" t="s">
+      <c r="A135" s="14"/>
+      <c r="B135" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C135" s="14"/>
+      <c r="C135" s="15"/>
     </row>
     <row r="136" ht="12.0" customHeight="1">
-      <c r="A136" s="13"/>
-      <c r="B136" s="13" t="s">
+      <c r="A136" s="14"/>
+      <c r="B136" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C136" s="14" t="s">
+      <c r="C136" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="137" ht="12.0" customHeight="1">
+      <c r="A137" s="14"/>
+      <c r="B137" s="14" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="137" ht="12.0" customHeight="1">
-      <c r="A137" s="13"/>
-      <c r="B137" s="13" t="s">
+      <c r="C137" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C137" s="15" t="s">
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="14"/>
+      <c r="B138" s="17" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="13"/>
-      <c r="B138" s="16" t="s">
+      <c r="C138" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C138" s="17" t="s">
+    </row>
+    <row r="139" ht="12.0" customHeight="1">
+      <c r="A139" s="14"/>
+      <c r="B139" s="14"/>
+      <c r="C139" s="15"/>
+    </row>
+    <row r="140" ht="12.0" customHeight="1">
+      <c r="A140" s="14" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="139" ht="12.0" customHeight="1">
-      <c r="A139" s="13"/>
-      <c r="B139" s="13"/>
-      <c r="C139" s="14"/>
-    </row>
-    <row r="140" ht="12.0" customHeight="1">
-      <c r="A140" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B140" s="13"/>
-      <c r="C140" s="14"/>
+      <c r="B140" s="14"/>
+      <c r="C140" s="15"/>
     </row>
     <row r="141" ht="12.0" customHeight="1">
-      <c r="A141" s="13"/>
-      <c r="B141" s="13" t="s">
+      <c r="A141" s="14"/>
+      <c r="B141" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C141" s="14" t="s">
-        <v>54</v>
+      <c r="C141" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="142" ht="12.0" customHeight="1">
-      <c r="A142" s="13"/>
-      <c r="B142" s="13" t="s">
+      <c r="A142" s="14"/>
+      <c r="B142" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C142" s="14" t="s">
+      <c r="C142" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="143" ht="12.0" customHeight="1">
-      <c r="A143" s="13"/>
-      <c r="B143" s="13" t="s">
+      <c r="A143" s="14"/>
+      <c r="B143" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C143" s="12">
@@ -2816,72 +2805,72 @@
       </c>
     </row>
     <row r="144" ht="12.0" customHeight="1">
-      <c r="A144" s="13"/>
-      <c r="B144" s="13" t="s">
+      <c r="A144" s="14"/>
+      <c r="B144" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C144" s="14"/>
+      <c r="C144" s="15"/>
     </row>
     <row r="145" ht="12.0" customHeight="1">
-      <c r="A145" s="13"/>
-      <c r="B145" s="13" t="s">
+      <c r="A145" s="14"/>
+      <c r="B145" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C145" s="14" t="s">
+      <c r="C145" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="146" ht="12.0" customHeight="1">
+      <c r="A146" s="14"/>
+      <c r="B146" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C146" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="14"/>
+      <c r="B147" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C147" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="148" ht="12.0" customHeight="1">
+      <c r="A148" s="14"/>
+      <c r="B148" s="14"/>
+      <c r="C148" s="15"/>
+    </row>
+    <row r="149" ht="12.0" customHeight="1">
+      <c r="A149" s="14" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="146" ht="12.0" customHeight="1">
-      <c r="A146" s="13"/>
-      <c r="B146" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C146" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="13"/>
-      <c r="B147" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C147" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="148" ht="12.0" customHeight="1">
-      <c r="A148" s="13"/>
-      <c r="B148" s="13"/>
-      <c r="C148" s="14"/>
-    </row>
-    <row r="149" ht="12.0" customHeight="1">
-      <c r="A149" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B149" s="13"/>
-      <c r="C149" s="14"/>
+      <c r="B149" s="14"/>
+      <c r="C149" s="15"/>
     </row>
     <row r="150" ht="12.0" customHeight="1">
-      <c r="A150" s="13"/>
-      <c r="B150" s="13" t="s">
+      <c r="A150" s="14"/>
+      <c r="B150" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C150" s="14" t="s">
-        <v>54</v>
+      <c r="C150" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="151" ht="12.0" customHeight="1">
-      <c r="A151" s="13"/>
-      <c r="B151" s="13" t="s">
+      <c r="A151" s="14"/>
+      <c r="B151" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C151" s="14" t="s">
+      <c r="C151" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="152" ht="12.0" customHeight="1">
-      <c r="A152" s="13"/>
-      <c r="B152" s="13" t="s">
+      <c r="A152" s="14"/>
+      <c r="B152" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C152" s="12">
@@ -2889,72 +2878,72 @@
       </c>
     </row>
     <row r="153" ht="12.0" customHeight="1">
-      <c r="A153" s="13"/>
-      <c r="B153" s="13" t="s">
+      <c r="A153" s="14"/>
+      <c r="B153" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C153" s="14"/>
+      <c r="C153" s="15"/>
     </row>
     <row r="154" ht="12.0" customHeight="1">
-      <c r="A154" s="13"/>
-      <c r="B154" s="13" t="s">
+      <c r="A154" s="14"/>
+      <c r="B154" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C154" s="14" t="s">
+      <c r="C154" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="155" ht="12.0" customHeight="1">
+      <c r="A155" s="14"/>
+      <c r="B155" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="14"/>
+      <c r="B156" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C156" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="157" ht="12.0" customHeight="1">
+      <c r="A157" s="14"/>
+      <c r="B157" s="14"/>
+      <c r="C157" s="15"/>
+    </row>
+    <row r="158" ht="12.0" customHeight="1">
+      <c r="A158" s="14" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="155" ht="12.0" customHeight="1">
-      <c r="A155" s="13"/>
-      <c r="B155" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C155" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="13"/>
-      <c r="B156" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C156" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="157" ht="12.0" customHeight="1">
-      <c r="A157" s="13"/>
-      <c r="B157" s="13"/>
-      <c r="C157" s="14"/>
-    </row>
-    <row r="158" ht="12.0" customHeight="1">
-      <c r="A158" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B158" s="13"/>
-      <c r="C158" s="14"/>
+      <c r="B158" s="14"/>
+      <c r="C158" s="15"/>
     </row>
     <row r="159" ht="12.0" customHeight="1">
-      <c r="A159" s="13"/>
-      <c r="B159" s="13" t="s">
+      <c r="A159" s="14"/>
+      <c r="B159" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C159" s="14" t="s">
-        <v>54</v>
+      <c r="C159" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="160" ht="12.0" customHeight="1">
-      <c r="A160" s="13"/>
-      <c r="B160" s="13" t="s">
+      <c r="A160" s="14"/>
+      <c r="B160" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C160" s="14" t="s">
+      <c r="C160" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="161" ht="12.0" customHeight="1">
-      <c r="A161" s="13"/>
-      <c r="B161" s="13" t="s">
+      <c r="A161" s="14"/>
+      <c r="B161" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C161" s="12">
@@ -2962,72 +2951,72 @@
       </c>
     </row>
     <row r="162" ht="12.0" customHeight="1">
-      <c r="A162" s="13"/>
-      <c r="B162" s="13" t="s">
+      <c r="A162" s="14"/>
+      <c r="B162" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C162" s="14"/>
+      <c r="C162" s="15"/>
     </row>
     <row r="163" ht="12.0" customHeight="1">
-      <c r="A163" s="13"/>
-      <c r="B163" s="13" t="s">
+      <c r="A163" s="14"/>
+      <c r="B163" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C163" s="14" t="s">
+      <c r="C163" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="164" ht="12.0" customHeight="1">
+      <c r="A164" s="14"/>
+      <c r="B164" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C164" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="14"/>
+      <c r="B165" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C165" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="166" ht="12.0" customHeight="1">
+      <c r="A166" s="14"/>
+      <c r="B166" s="14"/>
+      <c r="C166" s="15"/>
+    </row>
+    <row r="167" ht="12.0" customHeight="1">
+      <c r="A167" s="14" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="164" ht="12.0" customHeight="1">
-      <c r="A164" s="13"/>
-      <c r="B164" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C164" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="13"/>
-      <c r="B165" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C165" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="166" ht="12.0" customHeight="1">
-      <c r="A166" s="13"/>
-      <c r="B166" s="13"/>
-      <c r="C166" s="14"/>
-    </row>
-    <row r="167" ht="12.0" customHeight="1">
-      <c r="A167" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B167" s="13"/>
-      <c r="C167" s="14"/>
+      <c r="B167" s="14"/>
+      <c r="C167" s="15"/>
     </row>
     <row r="168" ht="12.0" customHeight="1">
-      <c r="A168" s="13"/>
-      <c r="B168" s="13" t="s">
+      <c r="A168" s="14"/>
+      <c r="B168" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C168" s="14" t="s">
-        <v>54</v>
+      <c r="C168" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="169" ht="12.0" customHeight="1">
-      <c r="A169" s="13"/>
-      <c r="B169" s="13" t="s">
+      <c r="A169" s="14"/>
+      <c r="B169" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C169" s="14" t="s">
+      <c r="C169" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="170" ht="12.0" customHeight="1">
-      <c r="A170" s="13"/>
-      <c r="B170" s="13" t="s">
+      <c r="A170" s="14"/>
+      <c r="B170" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C170" s="12">
@@ -3035,72 +3024,72 @@
       </c>
     </row>
     <row r="171" ht="12.0" customHeight="1">
-      <c r="A171" s="13"/>
-      <c r="B171" s="13" t="s">
+      <c r="A171" s="14"/>
+      <c r="B171" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C171" s="14"/>
+      <c r="C171" s="15"/>
     </row>
     <row r="172" ht="12.0" customHeight="1">
-      <c r="A172" s="13"/>
-      <c r="B172" s="13" t="s">
+      <c r="A172" s="14"/>
+      <c r="B172" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C172" s="14" t="s">
+      <c r="C172" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="173" ht="12.0" customHeight="1">
+      <c r="A173" s="14"/>
+      <c r="B173" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C173" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="14"/>
+      <c r="B174" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C174" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="175" ht="12.0" customHeight="1">
+      <c r="A175" s="14"/>
+      <c r="B175" s="14"/>
+      <c r="C175" s="15"/>
+    </row>
+    <row r="176" ht="12.0" customHeight="1">
+      <c r="A176" s="14" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="173" ht="12.0" customHeight="1">
-      <c r="A173" s="13"/>
-      <c r="B173" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C173" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="13"/>
-      <c r="B174" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C174" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="175" ht="12.0" customHeight="1">
-      <c r="A175" s="13"/>
-      <c r="B175" s="13"/>
-      <c r="C175" s="14"/>
-    </row>
-    <row r="176" ht="12.0" customHeight="1">
-      <c r="A176" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B176" s="13"/>
-      <c r="C176" s="14"/>
+      <c r="B176" s="14"/>
+      <c r="C176" s="15"/>
     </row>
     <row r="177" ht="12.0" customHeight="1">
-      <c r="A177" s="13"/>
-      <c r="B177" s="13" t="s">
+      <c r="A177" s="14"/>
+      <c r="B177" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C177" s="14" t="s">
-        <v>54</v>
+      <c r="C177" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="178" ht="12.0" customHeight="1">
-      <c r="A178" s="13"/>
-      <c r="B178" s="13" t="s">
+      <c r="A178" s="14"/>
+      <c r="B178" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C178" s="14" t="s">
+      <c r="C178" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="179" ht="12.0" customHeight="1">
-      <c r="A179" s="13"/>
-      <c r="B179" s="13" t="s">
+      <c r="A179" s="14"/>
+      <c r="B179" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C179" s="12">
@@ -3108,72 +3097,72 @@
       </c>
     </row>
     <row r="180" ht="12.0" customHeight="1">
-      <c r="A180" s="13"/>
-      <c r="B180" s="13" t="s">
+      <c r="A180" s="14"/>
+      <c r="B180" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C180" s="14"/>
+      <c r="C180" s="15"/>
     </row>
     <row r="181" ht="12.0" customHeight="1">
-      <c r="A181" s="13"/>
-      <c r="B181" s="13" t="s">
+      <c r="A181" s="14"/>
+      <c r="B181" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C181" s="14" t="s">
+      <c r="C181" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="182" ht="12.0" customHeight="1">
+      <c r="A182" s="14"/>
+      <c r="B182" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C182" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="A183" s="14"/>
+      <c r="B183" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C183" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="184" ht="12.0" customHeight="1">
+      <c r="A184" s="14"/>
+      <c r="B184" s="14"/>
+      <c r="C184" s="15"/>
+    </row>
+    <row r="185" ht="12.0" customHeight="1">
+      <c r="A185" s="14" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="182" ht="12.0" customHeight="1">
-      <c r="A182" s="13"/>
-      <c r="B182" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C182" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="13"/>
-      <c r="B183" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C183" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="184" ht="12.0" customHeight="1">
-      <c r="A184" s="13"/>
-      <c r="B184" s="13"/>
-      <c r="C184" s="14"/>
-    </row>
-    <row r="185" ht="12.0" customHeight="1">
-      <c r="A185" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B185" s="13"/>
-      <c r="C185" s="14"/>
+      <c r="B185" s="14"/>
+      <c r="C185" s="15"/>
     </row>
     <row r="186" ht="12.0" customHeight="1">
-      <c r="A186" s="13"/>
-      <c r="B186" s="13" t="s">
+      <c r="A186" s="14"/>
+      <c r="B186" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C186" s="14" t="s">
-        <v>54</v>
+      <c r="C186" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="187" ht="12.0" customHeight="1">
-      <c r="A187" s="13"/>
-      <c r="B187" s="13" t="s">
+      <c r="A187" s="14"/>
+      <c r="B187" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C187" s="14" t="s">
+      <c r="C187" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="188" ht="12.0" customHeight="1">
-      <c r="A188" s="13"/>
-      <c r="B188" s="13" t="s">
+      <c r="A188" s="14"/>
+      <c r="B188" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C188" s="12">
@@ -3181,72 +3170,72 @@
       </c>
     </row>
     <row r="189" ht="12.0" customHeight="1">
-      <c r="A189" s="13"/>
-      <c r="B189" s="13" t="s">
+      <c r="A189" s="14"/>
+      <c r="B189" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C189" s="14"/>
+      <c r="C189" s="15"/>
     </row>
     <row r="190" ht="12.0" customHeight="1">
-      <c r="A190" s="13"/>
-      <c r="B190" s="13" t="s">
+      <c r="A190" s="14"/>
+      <c r="B190" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C190" s="14" t="s">
+      <c r="C190" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="191" ht="12.0" customHeight="1">
+      <c r="A191" s="14"/>
+      <c r="B191" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C191" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="A192" s="14"/>
+      <c r="B192" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C192" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="193" ht="12.0" customHeight="1">
+      <c r="A193" s="14"/>
+      <c r="B193" s="14"/>
+      <c r="C193" s="15"/>
+    </row>
+    <row r="194" ht="12.0" customHeight="1">
+      <c r="A194" s="14" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="191" ht="12.0" customHeight="1">
-      <c r="A191" s="13"/>
-      <c r="B191" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C191" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="13"/>
-      <c r="B192" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C192" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="193" ht="12.0" customHeight="1">
-      <c r="A193" s="13"/>
-      <c r="B193" s="13"/>
-      <c r="C193" s="14"/>
-    </row>
-    <row r="194" ht="12.0" customHeight="1">
-      <c r="A194" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B194" s="13"/>
-      <c r="C194" s="14"/>
+      <c r="B194" s="14"/>
+      <c r="C194" s="15"/>
     </row>
     <row r="195" ht="12.0" customHeight="1">
-      <c r="A195" s="13"/>
-      <c r="B195" s="13" t="s">
+      <c r="A195" s="14"/>
+      <c r="B195" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C195" s="14" t="s">
-        <v>54</v>
+      <c r="C195" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="196" ht="12.0" customHeight="1">
-      <c r="A196" s="13"/>
-      <c r="B196" s="13" t="s">
+      <c r="A196" s="14"/>
+      <c r="B196" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C196" s="14" t="s">
+      <c r="C196" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="197" ht="12.0" customHeight="1">
-      <c r="A197" s="13"/>
-      <c r="B197" s="13" t="s">
+      <c r="A197" s="14"/>
+      <c r="B197" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C197" s="12">
@@ -3254,72 +3243,72 @@
       </c>
     </row>
     <row r="198" ht="12.0" customHeight="1">
-      <c r="A198" s="13"/>
-      <c r="B198" s="13" t="s">
+      <c r="A198" s="14"/>
+      <c r="B198" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C198" s="14"/>
+      <c r="C198" s="15"/>
     </row>
     <row r="199" ht="12.0" customHeight="1">
-      <c r="A199" s="13"/>
-      <c r="B199" s="13" t="s">
+      <c r="A199" s="14"/>
+      <c r="B199" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C199" s="14" t="s">
+      <c r="C199" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="200" ht="12.0" customHeight="1">
+      <c r="A200" s="14"/>
+      <c r="B200" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C200" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="A201" s="14"/>
+      <c r="B201" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C201" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="202" ht="12.0" customHeight="1">
+      <c r="A202" s="14"/>
+      <c r="B202" s="14"/>
+      <c r="C202" s="15"/>
+    </row>
+    <row r="203" ht="12.0" customHeight="1">
+      <c r="A203" s="14" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="200" ht="12.0" customHeight="1">
-      <c r="A200" s="13"/>
-      <c r="B200" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C200" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="13"/>
-      <c r="B201" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C201" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="202" ht="12.0" customHeight="1">
-      <c r="A202" s="13"/>
-      <c r="B202" s="13"/>
-      <c r="C202" s="14"/>
-    </row>
-    <row r="203" ht="12.0" customHeight="1">
-      <c r="A203" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B203" s="13"/>
-      <c r="C203" s="14"/>
+      <c r="B203" s="14"/>
+      <c r="C203" s="15"/>
     </row>
     <row r="204" ht="12.0" customHeight="1">
-      <c r="A204" s="13"/>
-      <c r="B204" s="13" t="s">
+      <c r="A204" s="14"/>
+      <c r="B204" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C204" s="14" t="s">
-        <v>54</v>
+      <c r="C204" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="205" ht="12.0" customHeight="1">
-      <c r="A205" s="13"/>
-      <c r="B205" s="13" t="s">
+      <c r="A205" s="14"/>
+      <c r="B205" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C205" s="14" t="s">
+      <c r="C205" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="206" ht="12.0" customHeight="1">
-      <c r="A206" s="13"/>
-      <c r="B206" s="13" t="s">
+      <c r="A206" s="14"/>
+      <c r="B206" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C206" s="12">
@@ -3327,72 +3316,72 @@
       </c>
     </row>
     <row r="207" ht="12.0" customHeight="1">
-      <c r="A207" s="13"/>
-      <c r="B207" s="13" t="s">
+      <c r="A207" s="14"/>
+      <c r="B207" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C207" s="14"/>
+      <c r="C207" s="15"/>
     </row>
     <row r="208" ht="12.0" customHeight="1">
-      <c r="A208" s="13"/>
-      <c r="B208" s="13" t="s">
+      <c r="A208" s="14"/>
+      <c r="B208" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C208" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="209" ht="12.0" customHeight="1">
+      <c r="A209" s="14"/>
+      <c r="B209" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C209" s="20" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="209" ht="12.0" customHeight="1">
-      <c r="A209" s="13"/>
-      <c r="B209" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C209" s="20" t="s">
+    <row r="210" ht="15.75" customHeight="1">
+      <c r="A210" s="14"/>
+      <c r="B210" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C210" s="18" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="13"/>
-      <c r="B210" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C210" s="21" t="s">
+    <row r="211" ht="12.0" customHeight="1">
+      <c r="A211" s="14"/>
+      <c r="B211" s="14"/>
+      <c r="C211" s="15"/>
+    </row>
+    <row r="212" ht="12.0" customHeight="1">
+      <c r="A212" s="14" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="211" ht="12.0" customHeight="1">
-      <c r="A211" s="13"/>
-      <c r="B211" s="13"/>
-      <c r="C211" s="14"/>
-    </row>
-    <row r="212" ht="12.0" customHeight="1">
-      <c r="A212" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B212" s="13"/>
-      <c r="C212" s="14"/>
+      <c r="B212" s="14"/>
+      <c r="C212" s="15"/>
     </row>
     <row r="213" ht="12.0" customHeight="1">
-      <c r="A213" s="13"/>
-      <c r="B213" s="13" t="s">
+      <c r="A213" s="14"/>
+      <c r="B213" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C213" s="14" t="s">
-        <v>54</v>
+      <c r="C213" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="214" ht="12.0" customHeight="1">
-      <c r="A214" s="13"/>
-      <c r="B214" s="13" t="s">
+      <c r="A214" s="14"/>
+      <c r="B214" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C214" s="14" t="s">
+      <c r="C214" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="215" ht="12.0" customHeight="1">
-      <c r="A215" s="13"/>
-      <c r="B215" s="13" t="s">
+      <c r="A215" s="14"/>
+      <c r="B215" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C215" s="12">
@@ -3400,72 +3389,72 @@
       </c>
     </row>
     <row r="216" ht="12.0" customHeight="1">
-      <c r="A216" s="13"/>
-      <c r="B216" s="13" t="s">
+      <c r="A216" s="14"/>
+      <c r="B216" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C216" s="14"/>
+      <c r="C216" s="15"/>
     </row>
     <row r="217" ht="12.0" customHeight="1">
-      <c r="A217" s="13"/>
-      <c r="B217" s="13" t="s">
+      <c r="A217" s="14"/>
+      <c r="B217" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C217" s="19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="218" ht="12.0" customHeight="1">
+      <c r="A218" s="14"/>
+      <c r="B218" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C218" s="20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="219" ht="15.75" customHeight="1">
+      <c r="A219" s="14"/>
+      <c r="B219" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C219" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="220" ht="12.0" customHeight="1">
+      <c r="A220" s="14"/>
+      <c r="B220" s="14"/>
+      <c r="C220" s="15"/>
+    </row>
+    <row r="221" ht="12.0" customHeight="1">
+      <c r="A221" s="14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="218" ht="12.0" customHeight="1">
-      <c r="A218" s="13"/>
-      <c r="B218" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C218" s="20" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="13"/>
-      <c r="B219" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C219" s="21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="220" ht="12.0" customHeight="1">
-      <c r="A220" s="13"/>
-      <c r="B220" s="13"/>
-      <c r="C220" s="14"/>
-    </row>
-    <row r="221" ht="12.0" customHeight="1">
-      <c r="A221" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B221" s="13"/>
-      <c r="C221" s="14"/>
+      <c r="B221" s="14"/>
+      <c r="C221" s="15"/>
     </row>
     <row r="222" ht="12.0" customHeight="1">
-      <c r="A222" s="13"/>
-      <c r="B222" s="13" t="s">
+      <c r="A222" s="14"/>
+      <c r="B222" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C222" s="14" t="s">
-        <v>54</v>
+      <c r="C222" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="223" ht="12.0" customHeight="1">
-      <c r="A223" s="13"/>
-      <c r="B223" s="13" t="s">
+      <c r="A223" s="14"/>
+      <c r="B223" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C223" s="14" t="s">
+      <c r="C223" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="224" ht="12.0" customHeight="1">
-      <c r="A224" s="13"/>
-      <c r="B224" s="13" t="s">
+      <c r="A224" s="14"/>
+      <c r="B224" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C224" s="12">
@@ -3473,72 +3462,72 @@
       </c>
     </row>
     <row r="225" ht="12.0" customHeight="1">
-      <c r="A225" s="13"/>
-      <c r="B225" s="13" t="s">
+      <c r="A225" s="14"/>
+      <c r="B225" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C225" s="14"/>
+      <c r="C225" s="15"/>
     </row>
     <row r="226" ht="12.0" customHeight="1">
-      <c r="A226" s="13"/>
-      <c r="B226" s="13" t="s">
+      <c r="A226" s="14"/>
+      <c r="B226" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C226" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="227" ht="15.75" customHeight="1">
+      <c r="A227" s="14"/>
+      <c r="B227" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C227" s="20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="228" ht="15.75" customHeight="1">
+      <c r="A228" s="14"/>
+      <c r="B228" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C228" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="229" ht="12.0" customHeight="1">
+      <c r="A229" s="14"/>
+      <c r="B229" s="14"/>
+      <c r="C229" s="15"/>
+    </row>
+    <row r="230" ht="12.0" customHeight="1">
+      <c r="A230" s="14" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="13"/>
-      <c r="B227" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C227" s="20" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="13"/>
-      <c r="B228" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C228" s="21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="229" ht="12.0" customHeight="1">
-      <c r="A229" s="13"/>
-      <c r="B229" s="13"/>
-      <c r="C229" s="14"/>
-    </row>
-    <row r="230" ht="12.0" customHeight="1">
-      <c r="A230" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B230" s="13"/>
-      <c r="C230" s="14"/>
+      <c r="B230" s="14"/>
+      <c r="C230" s="15"/>
     </row>
     <row r="231" ht="12.0" customHeight="1">
-      <c r="A231" s="13"/>
-      <c r="B231" s="13" t="s">
+      <c r="A231" s="14"/>
+      <c r="B231" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C231" s="14" t="s">
-        <v>54</v>
+      <c r="C231" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="232" ht="12.0" customHeight="1">
-      <c r="A232" s="13"/>
-      <c r="B232" s="13" t="s">
+      <c r="A232" s="14"/>
+      <c r="B232" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C232" s="14" t="s">
+      <c r="C232" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="233" ht="12.0" customHeight="1">
-      <c r="A233" s="13"/>
-      <c r="B233" s="13" t="s">
+      <c r="A233" s="14"/>
+      <c r="B233" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C233" s="12">
@@ -3546,72 +3535,72 @@
       </c>
     </row>
     <row r="234" ht="12.0" customHeight="1">
-      <c r="A234" s="13"/>
-      <c r="B234" s="13" t="s">
+      <c r="A234" s="14"/>
+      <c r="B234" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C234" s="14"/>
+      <c r="C234" s="15"/>
     </row>
     <row r="235" ht="12.0" customHeight="1">
-      <c r="A235" s="13"/>
-      <c r="B235" s="13" t="s">
+      <c r="A235" s="14"/>
+      <c r="B235" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C235" s="14" t="s">
+      <c r="C235" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="236" ht="12.0" customHeight="1">
+      <c r="A236" s="14"/>
+      <c r="B236" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C236" s="16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="236" ht="12.0" customHeight="1">
-      <c r="A236" s="13"/>
-      <c r="B236" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C236" s="15" t="s">
+    <row r="237" ht="15.75" customHeight="1">
+      <c r="A237" s="14"/>
+      <c r="B237" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C237" s="21" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="13"/>
-      <c r="B237" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C237" s="22" t="s">
+    <row r="238" ht="12.0" customHeight="1">
+      <c r="A238" s="14"/>
+      <c r="B238" s="14"/>
+      <c r="C238" s="15"/>
+    </row>
+    <row r="239" ht="12.0" customHeight="1">
+      <c r="A239" s="14" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="238" ht="12.0" customHeight="1">
-      <c r="A238" s="13"/>
-      <c r="B238" s="13"/>
-      <c r="C238" s="14"/>
-    </row>
-    <row r="239" ht="12.0" customHeight="1">
-      <c r="A239" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B239" s="13"/>
-      <c r="C239" s="14"/>
+      <c r="B239" s="14"/>
+      <c r="C239" s="15"/>
     </row>
     <row r="240" ht="12.0" customHeight="1">
-      <c r="A240" s="13"/>
-      <c r="B240" s="13" t="s">
+      <c r="A240" s="14"/>
+      <c r="B240" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C240" s="14" t="s">
-        <v>54</v>
+      <c r="C240" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="241" ht="12.0" customHeight="1">
-      <c r="A241" s="13"/>
-      <c r="B241" s="13" t="s">
+      <c r="A241" s="14"/>
+      <c r="B241" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C241" s="14" t="s">
+      <c r="C241" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="242" ht="12.0" customHeight="1">
-      <c r="A242" s="13"/>
-      <c r="B242" s="13" t="s">
+      <c r="A242" s="14"/>
+      <c r="B242" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C242" s="12">
@@ -3619,72 +3608,72 @@
       </c>
     </row>
     <row r="243" ht="12.0" customHeight="1">
-      <c r="A243" s="13"/>
-      <c r="B243" s="13" t="s">
+      <c r="A243" s="14"/>
+      <c r="B243" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C243" s="14"/>
+      <c r="C243" s="15"/>
     </row>
     <row r="244" ht="12.0" customHeight="1">
-      <c r="A244" s="13"/>
-      <c r="B244" s="13" t="s">
+      <c r="A244" s="14"/>
+      <c r="B244" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C244" s="14" t="s">
+      <c r="C244" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="245" ht="12.0" customHeight="1">
+      <c r="A245" s="14"/>
+      <c r="B245" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="246" ht="15.75" customHeight="1">
+      <c r="A246" s="14"/>
+      <c r="B246" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C246" s="21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="247" ht="12.0" customHeight="1">
+      <c r="A247" s="14"/>
+      <c r="B247" s="14"/>
+      <c r="C247" s="15"/>
+    </row>
+    <row r="248" ht="12.0" customHeight="1">
+      <c r="A248" s="14" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="245" ht="12.0" customHeight="1">
-      <c r="A245" s="13"/>
-      <c r="B245" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C245" s="18" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="13"/>
-      <c r="B246" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C246" s="22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="247" ht="12.0" customHeight="1">
-      <c r="A247" s="13"/>
-      <c r="B247" s="13"/>
-      <c r="C247" s="14"/>
-    </row>
-    <row r="248" ht="12.0" customHeight="1">
-      <c r="A248" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B248" s="13"/>
-      <c r="C248" s="14"/>
+      <c r="B248" s="14"/>
+      <c r="C248" s="15"/>
     </row>
     <row r="249" ht="12.0" customHeight="1">
-      <c r="A249" s="13"/>
-      <c r="B249" s="13" t="s">
+      <c r="A249" s="14"/>
+      <c r="B249" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C249" s="14" t="s">
-        <v>54</v>
+      <c r="C249" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="250" ht="12.0" customHeight="1">
-      <c r="A250" s="13"/>
-      <c r="B250" s="13" t="s">
+      <c r="A250" s="14"/>
+      <c r="B250" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C250" s="14" t="s">
+      <c r="C250" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="251" ht="12.0" customHeight="1">
-      <c r="A251" s="13"/>
-      <c r="B251" s="13" t="s">
+      <c r="A251" s="14"/>
+      <c r="B251" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C251" s="12">
@@ -3692,72 +3681,72 @@
       </c>
     </row>
     <row r="252" ht="12.0" customHeight="1">
-      <c r="A252" s="13"/>
-      <c r="B252" s="13" t="s">
+      <c r="A252" s="14"/>
+      <c r="B252" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C252" s="14"/>
+      <c r="C252" s="15"/>
     </row>
     <row r="253" ht="12.0" customHeight="1">
-      <c r="A253" s="13"/>
-      <c r="B253" s="13" t="s">
+      <c r="A253" s="14"/>
+      <c r="B253" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C253" s="14" t="s">
+      <c r="C253" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="254" ht="12.0" customHeight="1">
+      <c r="A254" s="14"/>
+      <c r="B254" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C254" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
+      <c r="A255" s="14"/>
+      <c r="B255" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C255" s="21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="256" ht="12.0" customHeight="1">
+      <c r="A256" s="14"/>
+      <c r="B256" s="14"/>
+      <c r="C256" s="15"/>
+    </row>
+    <row r="257" ht="12.0" customHeight="1">
+      <c r="A257" s="14" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="254" ht="12.0" customHeight="1">
-      <c r="A254" s="13"/>
-      <c r="B254" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C254" s="18" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="13"/>
-      <c r="B255" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C255" s="22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="256" ht="12.0" customHeight="1">
-      <c r="A256" s="13"/>
-      <c r="B256" s="13"/>
-      <c r="C256" s="14"/>
-    </row>
-    <row r="257" ht="12.0" customHeight="1">
-      <c r="A257" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B257" s="13"/>
-      <c r="C257" s="14"/>
+      <c r="B257" s="14"/>
+      <c r="C257" s="15"/>
     </row>
     <row r="258" ht="12.0" customHeight="1">
-      <c r="A258" s="13"/>
-      <c r="B258" s="13" t="s">
+      <c r="A258" s="14"/>
+      <c r="B258" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C258" s="14" t="s">
-        <v>54</v>
+      <c r="C258" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="259" ht="12.0" customHeight="1">
-      <c r="A259" s="13"/>
-      <c r="B259" s="13" t="s">
+      <c r="A259" s="14"/>
+      <c r="B259" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C259" s="14" t="s">
+      <c r="C259" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="260" ht="12.0" customHeight="1">
-      <c r="A260" s="13"/>
-      <c r="B260" s="13" t="s">
+      <c r="A260" s="14"/>
+      <c r="B260" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C260" s="12">
@@ -3765,37 +3754,37 @@
       </c>
     </row>
     <row r="261" ht="12.0" customHeight="1">
-      <c r="A261" s="13"/>
-      <c r="B261" s="13" t="s">
+      <c r="A261" s="14"/>
+      <c r="B261" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C261" s="14"/>
+      <c r="C261" s="15"/>
     </row>
     <row r="262" ht="12.0" customHeight="1">
-      <c r="A262" s="13"/>
-      <c r="B262" s="13" t="s">
+      <c r="A262" s="14"/>
+      <c r="B262" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C262" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="263" ht="12.0" customHeight="1">
-      <c r="A263" s="13"/>
-      <c r="B263" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C263" s="18" t="s">
+      <c r="A263" s="14"/>
+      <c r="B263" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="264" ht="15.75" customHeight="1">
+      <c r="A264" s="14"/>
+      <c r="B264" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C264" s="21" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="13"/>
-      <c r="B264" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C264" s="22" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="265" ht="12.0" customHeight="1">
